--- a/output/roomself_excel/12624.xlsx
+++ b/output/roomself_excel/12624.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>886493</v>
+        <v>94678</v>
       </c>
       <c r="D2" t="n">
-        <v>9612</v>
+        <v>3052</v>
       </c>
       <c r="E2" t="n">
-        <v>1267</v>
+        <v>392</v>
       </c>
       <c r="F2" t="n">
-        <v>813</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>132132</v>
+        <v>90192</v>
       </c>
       <c r="D3" t="n">
-        <v>2992</v>
+        <v>2648</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>331892</v>
+        <v>132132</v>
       </c>
       <c r="D4" t="n">
-        <v>8652</v>
+        <v>2992</v>
       </c>
       <c r="E4" t="n">
-        <v>909</v>
+        <v>286</v>
       </c>
       <c r="F4" t="n">
-        <v>813</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43896</v>
+        <v>84456</v>
       </c>
       <c r="D5" t="n">
-        <v>1912</v>
+        <v>2328</v>
       </c>
       <c r="E5" t="n">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="F5" t="n">
-        <v>149</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9680</v>
+        <v>9682</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64889</v>
+        <v>7047</v>
       </c>
       <c r="D7" t="n">
-        <v>2136</v>
+        <v>672</v>
       </c>
       <c r="E7" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28527</v>
+        <v>28688</v>
       </c>
       <c r="D8" t="n">
-        <v>1472</v>
+        <v>1356</v>
       </c>
       <c r="E8" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10323</v>
+        <v>28525</v>
       </c>
       <c r="D9" t="n">
-        <v>816</v>
+        <v>1352</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>117</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>368675</v>
+        <v>86641</v>
       </c>
       <c r="D10" t="n">
-        <v>5056</v>
+        <v>3120</v>
       </c>
       <c r="E10" t="n">
-        <v>785</v>
+        <v>387</v>
       </c>
       <c r="F10" t="n">
-        <v>520</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -664,17 +664,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100536</v>
+        <v>41031</v>
       </c>
       <c r="D11" t="n">
-        <v>2672</v>
+        <v>1728</v>
       </c>
       <c r="E11" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>93412</v>
+        <v>886493</v>
       </c>
       <c r="D12" t="n">
-        <v>2512</v>
+        <v>9612</v>
       </c>
       <c r="E12" t="n">
-        <v>386</v>
+        <v>1267</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>813</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90192</v>
+        <v>331892</v>
       </c>
       <c r="D13" t="n">
-        <v>2648</v>
+        <v>8652</v>
       </c>
       <c r="E13" t="n">
-        <v>312</v>
+        <v>909</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>105964</v>
+        <v>43896</v>
       </c>
       <c r="D14" t="n">
-        <v>2796</v>
+        <v>1912</v>
       </c>
       <c r="E14" t="n">
-        <v>271</v>
+        <v>378</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84456</v>
+        <v>9680</v>
       </c>
       <c r="D15" t="n">
-        <v>2328</v>
+        <v>792</v>
       </c>
       <c r="E15" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>58286</v>
+        <v>64889</v>
       </c>
       <c r="D16" t="n">
-        <v>2148</v>
+        <v>2136</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28182</v>
+        <v>28527</v>
       </c>
       <c r="D17" t="n">
-        <v>1364</v>
+        <v>1472</v>
       </c>
       <c r="E17" t="n">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="F17" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11536</v>
+        <v>10323</v>
       </c>
       <c r="D18" t="n">
-        <v>860</v>
+        <v>816</v>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25933</v>
+        <v>368675</v>
       </c>
       <c r="D19" t="n">
-        <v>1544</v>
+        <v>5056</v>
       </c>
       <c r="E19" t="n">
-        <v>103</v>
+        <v>785</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20">
@@ -862,17 +862,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9682</v>
+        <v>100536</v>
       </c>
       <c r="D20" t="n">
-        <v>788</v>
+        <v>2672</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>264</v>
       </c>
       <c r="F20" t="n">
         <v>26</v>
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7047</v>
+        <v>93412</v>
       </c>
       <c r="D21" t="n">
-        <v>672</v>
+        <v>2512</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>86641</v>
+        <v>105964</v>
       </c>
       <c r="D22" t="n">
-        <v>3120</v>
+        <v>2796</v>
       </c>
       <c r="E22" t="n">
-        <v>387</v>
+        <v>271</v>
       </c>
       <c r="F22" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -928,14 +928,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28688</v>
+        <v>58286</v>
       </c>
       <c r="D23" t="n">
-        <v>1356</v>
+        <v>2148</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28525</v>
+        <v>28182</v>
       </c>
       <c r="D24" t="n">
-        <v>1352</v>
+        <v>1364</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30089</v>
+        <v>11536</v>
       </c>
       <c r="D25" t="n">
-        <v>2028</v>
+        <v>860</v>
       </c>
       <c r="E25" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>109365</v>
+        <v>25933</v>
       </c>
       <c r="D26" t="n">
-        <v>2648</v>
+        <v>1544</v>
       </c>
       <c r="E26" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>94678</v>
+        <v>30089</v>
       </c>
       <c r="D27" t="n">
-        <v>3052</v>
+        <v>2028</v>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41031</v>
+        <v>109365</v>
       </c>
       <c r="D28" t="n">
-        <v>1728</v>
+        <v>2648</v>
       </c>
       <c r="E28" t="n">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="F28" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">

--- a/output/roomself_excel/12624.xlsx
+++ b/output/roomself_excel/12624.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>3052</v>
       </c>
-      <c r="E2" t="n">
-        <v>392</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>241</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>366</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,23 @@
       <c r="D3" t="n">
         <v>2648</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>312</v>
       </c>
-      <c r="F3" t="n">
-        <v>26</v>
-      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,23 @@
       <c r="D4" t="n">
         <v>2992</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>286</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>25</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>2328</v>
       </c>
-      <c r="E5" t="n">
-        <v>332</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>302</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>276</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,23 @@
       <c r="D6" t="n">
         <v>788</v>
       </c>
-      <c r="E6" t="n">
-        <v>94</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,15 @@
       <c r="D7" t="n">
         <v>672</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +716,15 @@
       <c r="D8" t="n">
         <v>1356</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +741,15 @@
       <c r="D9" t="n">
         <v>1352</v>
       </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +766,31 @@
       <c r="D10" t="n">
         <v>3120</v>
       </c>
-      <c r="E10" t="n">
-        <v>387</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +807,23 @@
       <c r="D11" t="n">
         <v>1728</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>291</v>
       </c>
-      <c r="F11" t="n">
-        <v>26</v>
-      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +840,38 @@
       <c r="D12" t="n">
         <v>9612</v>
       </c>
-      <c r="E12" t="n">
-        <v>1267</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>813</v>
+        <v>1243</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>764</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1181</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +889,38 @@
       <c r="D13" t="n">
         <v>8652</v>
       </c>
-      <c r="E13" t="n">
-        <v>909</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>813</v>
+        <v>161</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>507</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>155</v>
+      </c>
+      <c r="M13" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -739,12 +938,31 @@
       <c r="D14" t="n">
         <v>1912</v>
       </c>
-      <c r="E14" t="n">
-        <v>378</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>149</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>124</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +979,15 @@
       <c r="D15" t="n">
         <v>792</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1004,23 @@
       <c r="D16" t="n">
         <v>2136</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>347</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>24</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1037,23 @@
       <c r="D17" t="n">
         <v>1472</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>257</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>24</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1070,31 @@
       <c r="D18" t="n">
         <v>816</v>
       </c>
-      <c r="E18" t="n">
-        <v>135</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>117</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>93</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1111,31 @@
       <c r="D19" t="n">
         <v>5056</v>
       </c>
-      <c r="E19" t="n">
-        <v>785</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>520</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>733</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1152,23 @@
       <c r="D20" t="n">
         <v>2672</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>264</v>
       </c>
-      <c r="F20" t="n">
-        <v>26</v>
-      </c>
+      <c r="G20" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1185,23 @@
       <c r="D21" t="n">
         <v>2512</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>386</v>
       </c>
-      <c r="F21" t="n">
-        <v>26</v>
-      </c>
+      <c r="G21" t="n">
+        <v>26</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1218,23 @@
       <c r="D22" t="n">
         <v>2796</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>271</v>
       </c>
-      <c r="F22" t="n">
-        <v>26</v>
-      </c>
+      <c r="G22" t="n">
+        <v>26</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1251,15 @@
       <c r="D23" t="n">
         <v>2148</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1276,15 @@
       <c r="D24" t="n">
         <v>1364</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1301,23 @@
       <c r="D25" t="n">
         <v>860</v>
       </c>
-      <c r="E25" t="n">
-        <v>112</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1334,15 @@
       <c r="D26" t="n">
         <v>1544</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1359,15 @@
       <c r="D27" t="n">
         <v>2028</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1384,23 @@
       <c r="D28" t="n">
         <v>2648</v>
       </c>
-      <c r="E28" t="n">
-        <v>345</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="G28" t="n">
+        <v>26</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1417,23 @@
       <c r="D29" t="n">
         <v>640</v>
       </c>
-      <c r="E29" t="n">
-        <v>65</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>26</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1450,23 @@
       <c r="D30" t="n">
         <v>672</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>73</v>
       </c>
-      <c r="F30" t="n">
-        <v>26</v>
-      </c>
+      <c r="G30" t="n">
+        <v>26</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1483,23 @@
       <c r="D31" t="n">
         <v>572</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>80</v>
       </c>
-      <c r="F31" t="n">
-        <v>26</v>
-      </c>
+      <c r="G31" t="n">
+        <v>26</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
